--- a/data/t2m_classification.xlsx
+++ b/data/t2m_classification.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fa6df288256b873d/t2m/py_code/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\t2m-project\t2m-pycode\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="13_ncr:1_{21992D63-61E8-46A5-8A53-EE10256A1BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80807420-8159-4A99-88B0-4E66A5701D02}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BDCAB0-3675-46A4-B231-A54C26918719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="new_stock_list" sheetId="1" r:id="rId1"/>
@@ -6436,7 +6436,7 @@
         <v>1822</v>
       </c>
       <c r="H2" t="str">
-        <f>VLOOKUP(D2,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D2,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
         <v>1804</v>
       </c>
       <c r="H3" t="str">
-        <f>VLOOKUP(D3,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D3,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -6491,9 +6491,9 @@
       <c r="G4" t="s">
         <v>1804</v>
       </c>
-      <c r="H4" t="e">
-        <f>VLOOKUP(D4,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H4" t="str">
+        <f>VLOOKUP(D4,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bán lẻ</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6519,9 +6519,9 @@
       <c r="G5" t="s">
         <v>1822</v>
       </c>
-      <c r="H5" t="e">
-        <f>VLOOKUP(D5,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H5" t="str">
+        <f>VLOOKUP(D5,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -6548,7 +6548,7 @@
         <v>1804</v>
       </c>
       <c r="H6" t="str">
-        <f>VLOOKUP(D6,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D6,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
         <v>1822</v>
       </c>
       <c r="H7" t="str">
-        <f>VLOOKUP(D7,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D7,name_map!$A$2:$C$33,3,0)</f>
         <v>Bảo hiểm</v>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
         <v>1804</v>
       </c>
       <c r="H8" t="str">
-        <f>VLOOKUP(D8,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D8,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -6632,7 +6632,7 @@
         <v>1804</v>
       </c>
       <c r="H9" t="str">
-        <f>VLOOKUP(D9,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D9,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -6660,7 +6660,7 @@
         <v>1804</v>
       </c>
       <c r="H10" t="str">
-        <f>VLOOKUP(D10,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D10,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
         <v>1804</v>
       </c>
       <c r="H11" t="str">
-        <f>VLOOKUP(D11,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D11,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
         <v>1804</v>
       </c>
       <c r="H12" t="str">
-        <f>VLOOKUP(D12,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D12,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
         <v>1804</v>
       </c>
       <c r="H13" t="str">
-        <f>VLOOKUP(D13,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D13,name_map!$A$2:$C$33,3,0)</f>
         <v>Thuỷ sản</v>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
         <v>1804</v>
       </c>
       <c r="H14" t="str">
-        <f>VLOOKUP(D14,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D14,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
         <v>1804</v>
       </c>
       <c r="H15" t="str">
-        <f>VLOOKUP(D15,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D15,name_map!$A$2:$C$33,3,0)</f>
         <v>Du lịch và DV</v>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
         <v>1804</v>
       </c>
       <c r="H16" t="str">
-        <f>VLOOKUP(D16,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D16,name_map!$A$2:$C$33,3,0)</f>
         <v>Dệt may</v>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
         <v>1804</v>
       </c>
       <c r="H17" t="str">
-        <f>VLOOKUP(D17,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D17,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -6883,9 +6883,9 @@
       <c r="G18" t="s">
         <v>1804</v>
       </c>
-      <c r="H18" t="e">
-        <f>VLOOKUP(D18,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H18" t="str">
+        <f>VLOOKUP(D18,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -6912,7 +6912,7 @@
         <v>1804</v>
       </c>
       <c r="H19" t="str">
-        <f>VLOOKUP(D19,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D19,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
         <v>1822</v>
       </c>
       <c r="H20" t="str">
-        <f>VLOOKUP(D20,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D20,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>1804</v>
       </c>
       <c r="H21" t="str">
-        <f>VLOOKUP(D21,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D21,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
         <v>1804</v>
       </c>
       <c r="H22" t="str">
-        <f>VLOOKUP(D22,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D22,name_map!$A$2:$C$33,3,0)</f>
         <v>Y tế</v>
       </c>
     </row>
@@ -7024,7 +7024,7 @@
         <v>1822</v>
       </c>
       <c r="H23" t="str">
-        <f>VLOOKUP(D23,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D23,name_map!$A$2:$C$33,3,0)</f>
         <v>Thuỷ sản</v>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
         <v>1804</v>
       </c>
       <c r="H24" t="str">
-        <f>VLOOKUP(D24,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D24,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -7080,7 +7080,7 @@
         <v>1804</v>
       </c>
       <c r="H25" t="str">
-        <f>VLOOKUP(D25,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D25,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
         <v>1804</v>
       </c>
       <c r="H26" t="str">
-        <f>VLOOKUP(D26,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D26,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -7135,9 +7135,9 @@
       <c r="G27" t="s">
         <v>1804</v>
       </c>
-      <c r="H27" t="e">
-        <f>VLOOKUP(D27,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H27" t="str">
+        <f>VLOOKUP(D27,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -7164,7 +7164,7 @@
         <v>1804</v>
       </c>
       <c r="H28" t="str">
-        <f>VLOOKUP(D28,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D28,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -7191,9 +7191,9 @@
       <c r="G29" t="s">
         <v>1804</v>
       </c>
-      <c r="H29" t="e">
-        <f>VLOOKUP(D29,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H29" t="str">
+        <f>VLOOKUP(D29,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -7220,7 +7220,7 @@
         <v>1804</v>
       </c>
       <c r="H30" t="str">
-        <f>VLOOKUP(D30,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D30,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
         <v>1804</v>
       </c>
       <c r="H31" t="str">
-        <f>VLOOKUP(D31,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D31,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
         <v>1804</v>
       </c>
       <c r="H32" t="str">
-        <f>VLOOKUP(D32,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D32,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
         <v>1804</v>
       </c>
       <c r="H33" t="str">
-        <f>VLOOKUP(D33,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D33,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
         <v>1822</v>
       </c>
       <c r="H34" t="str">
-        <f>VLOOKUP(D34,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D34,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -7360,7 +7360,7 @@
         <v>1804</v>
       </c>
       <c r="H35" t="str">
-        <f>VLOOKUP(D35,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D35,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -7388,7 +7388,7 @@
         <v>1804</v>
       </c>
       <c r="H36" t="str">
-        <f>VLOOKUP(D36,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D36,name_map!$A$2:$C$33,3,0)</f>
         <v>Công ty tài chính</v>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
         <v>1804</v>
       </c>
       <c r="H37" t="str">
-        <f>VLOOKUP(D37,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D37,name_map!$A$2:$C$33,3,0)</f>
         <v>BĐS KCN</v>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
         <v>1822</v>
       </c>
       <c r="H38" t="str">
-        <f>VLOOKUP(D38,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D38,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
         <v>1804</v>
       </c>
       <c r="H39" t="str">
-        <f>VLOOKUP(D39,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D39,name_map!$A$2:$C$33,3,0)</f>
         <v>Bảo hiểm</v>
       </c>
     </row>
@@ -7500,7 +7500,7 @@
         <v>1804</v>
       </c>
       <c r="H40" t="str">
-        <f>VLOOKUP(D40,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D40,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -7528,7 +7528,7 @@
         <v>1804</v>
       </c>
       <c r="H41" t="str">
-        <f>VLOOKUP(D41,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D41,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
         <v>1804</v>
       </c>
       <c r="H42" t="str">
-        <f>VLOOKUP(D42,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D42,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -7584,7 +7584,7 @@
         <v>1822</v>
       </c>
       <c r="H43" t="str">
-        <f>VLOOKUP(D43,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D43,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -7612,7 +7612,7 @@
         <v>1822</v>
       </c>
       <c r="H44" t="str">
-        <f>VLOOKUP(D44,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D44,name_map!$A$2:$C$33,3,0)</f>
         <v>Bảo hiểm</v>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
         <v>1804</v>
       </c>
       <c r="H45" t="str">
-        <f>VLOOKUP(D45,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D45,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -7668,7 +7668,7 @@
         <v>1822</v>
       </c>
       <c r="H46" t="str">
-        <f>VLOOKUP(D46,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D46,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -7696,7 +7696,7 @@
         <v>1804</v>
       </c>
       <c r="H47" t="str">
-        <f>VLOOKUP(D47,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D47,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
         <v>1804</v>
       </c>
       <c r="H48" t="str">
-        <f>VLOOKUP(D48,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D48,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -7752,7 +7752,7 @@
         <v>1804</v>
       </c>
       <c r="H49" t="str">
-        <f>VLOOKUP(D49,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D49,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
         <v>1822</v>
       </c>
       <c r="H50" t="str">
-        <f>VLOOKUP(D50,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D50,name_map!$A$2:$C$33,3,0)</f>
         <v>Dầu khí</v>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
         <v>1804</v>
       </c>
       <c r="H51" t="str">
-        <f>VLOOKUP(D51,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D51,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
         <v>1804</v>
       </c>
       <c r="H52" t="str">
-        <f>VLOOKUP(D52,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D52,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
         <v>1804</v>
       </c>
       <c r="H53" t="str">
-        <f>VLOOKUP(D53,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D53,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
         <v>1822</v>
       </c>
       <c r="H54" t="str">
-        <f>VLOOKUP(D54,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D54,name_map!$A$2:$C$33,3,0)</f>
         <v>Thép</v>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
         <v>1804</v>
       </c>
       <c r="H55" t="str">
-        <f>VLOOKUP(D55,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D55,name_map!$A$2:$C$33,3,0)</f>
         <v>Bảo hiểm</v>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
         <v>1822</v>
       </c>
       <c r="H56" t="str">
-        <f>VLOOKUP(D56,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D56,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -7976,7 +7976,7 @@
         <v>1804</v>
       </c>
       <c r="H57" t="str">
-        <f>VLOOKUP(D57,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D57,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -8004,7 +8004,7 @@
         <v>1804</v>
       </c>
       <c r="H58" t="str">
-        <f>VLOOKUP(D58,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D58,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -8032,7 +8032,7 @@
         <v>1804</v>
       </c>
       <c r="H59" t="str">
-        <f>VLOOKUP(D59,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D59,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -8060,7 +8060,7 @@
         <v>1822</v>
       </c>
       <c r="H60" t="str">
-        <f>VLOOKUP(D60,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D60,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -8088,7 +8088,7 @@
         <v>1804</v>
       </c>
       <c r="H61" t="str">
-        <f>VLOOKUP(D61,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D61,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -8116,7 +8116,7 @@
         <v>1804</v>
       </c>
       <c r="H62" t="str">
-        <f>VLOOKUP(D62,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D62,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -8144,7 +8144,7 @@
         <v>1822</v>
       </c>
       <c r="H63" t="str">
-        <f>VLOOKUP(D63,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D63,name_map!$A$2:$C$33,3,0)</f>
         <v>BĐS KCN</v>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
         <v>1804</v>
       </c>
       <c r="H64" t="str">
-        <f>VLOOKUP(D64,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D64,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
         <v>1822</v>
       </c>
       <c r="H65" t="str">
-        <f>VLOOKUP(D65,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D65,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -8227,9 +8227,9 @@
       <c r="G66" t="s">
         <v>1822</v>
       </c>
-      <c r="H66" t="e">
-        <f>VLOOKUP(D66,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H66" t="str">
+        <f>VLOOKUP(D66,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bán lẻ</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -8255,9 +8255,9 @@
       <c r="G67" t="s">
         <v>1804</v>
       </c>
-      <c r="H67" t="e">
-        <f>VLOOKUP(D67,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H67" t="str">
+        <f>VLOOKUP(D67,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -8283,9 +8283,9 @@
       <c r="G68" t="s">
         <v>1804</v>
       </c>
-      <c r="H68" t="e">
-        <f>VLOOKUP(D68,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H68" t="str">
+        <f>VLOOKUP(D68,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -8312,7 +8312,7 @@
         <v>1804</v>
       </c>
       <c r="H69" t="str">
-        <f>VLOOKUP(D69,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D69,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -8339,9 +8339,9 @@
       <c r="G70" t="s">
         <v>1804</v>
       </c>
-      <c r="H70" t="e">
-        <f>VLOOKUP(D70,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H70" t="str">
+        <f>VLOOKUP(D70,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -8367,9 +8367,9 @@
       <c r="G71" t="s">
         <v>1804</v>
       </c>
-      <c r="H71" t="e">
-        <f>VLOOKUP(D71,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H71" t="str">
+        <f>VLOOKUP(D71,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bán lẻ</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -8396,7 +8396,7 @@
         <v>1804</v>
       </c>
       <c r="H72" t="str">
-        <f>VLOOKUP(D72,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D72,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghệ</v>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
         <v>1804</v>
       </c>
       <c r="H73" t="str">
-        <f>VLOOKUP(D73,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D73,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -8452,7 +8452,7 @@
         <v>1804</v>
       </c>
       <c r="H74" t="str">
-        <f>VLOOKUP(D74,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D74,name_map!$A$2:$C$33,3,0)</f>
         <v>Thuỷ sản</v>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
         <v>1804</v>
       </c>
       <c r="H75" t="str">
-        <f>VLOOKUP(D75,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D75,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -8508,7 +8508,7 @@
         <v>1804</v>
       </c>
       <c r="H76" t="str">
-        <f>VLOOKUP(D76,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D76,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -8535,9 +8535,9 @@
       <c r="G77" t="s">
         <v>1822</v>
       </c>
-      <c r="H77" t="e">
-        <f>VLOOKUP(D77,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H77" t="str">
+        <f>VLOOKUP(D77,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -8563,9 +8563,9 @@
       <c r="G78" t="s">
         <v>1804</v>
       </c>
-      <c r="H78" t="e">
-        <f>VLOOKUP(D78,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H78" t="str">
+        <f>VLOOKUP(D78,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -8592,7 +8592,7 @@
         <v>1804</v>
       </c>
       <c r="H79" t="str">
-        <f>VLOOKUP(D79,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D79,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -8620,7 +8620,7 @@
         <v>1804</v>
       </c>
       <c r="H80" t="str">
-        <f>VLOOKUP(D80,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D80,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -8648,7 +8648,7 @@
         <v>1804</v>
       </c>
       <c r="H81" t="str">
-        <f>VLOOKUP(D81,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D81,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
         <v>1804</v>
       </c>
       <c r="H82" t="str">
-        <f>VLOOKUP(D82,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D82,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
         <v>1804</v>
       </c>
       <c r="H83" t="str">
-        <f>VLOOKUP(D83,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D83,name_map!$A$2:$C$33,3,0)</f>
         <v>Du lịch và DV</v>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
         <v>1804</v>
       </c>
       <c r="H84" t="str">
-        <f>VLOOKUP(D84,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D84,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -8760,7 +8760,7 @@
         <v>1804</v>
       </c>
       <c r="H85" t="str">
-        <f>VLOOKUP(D85,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D85,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -8788,7 +8788,7 @@
         <v>1804</v>
       </c>
       <c r="H86" t="str">
-        <f>VLOOKUP(D86,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D86,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -8816,7 +8816,7 @@
         <v>1804</v>
       </c>
       <c r="H87" t="str">
-        <f>VLOOKUP(D87,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D87,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
         <v>1804</v>
       </c>
       <c r="H88" t="str">
-        <f>VLOOKUP(D88,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D88,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
         <v>1822</v>
       </c>
       <c r="H89" t="str">
-        <f>VLOOKUP(D89,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D89,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
         <v>1804</v>
       </c>
       <c r="H90" t="str">
-        <f>VLOOKUP(D90,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D90,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -8927,9 +8927,9 @@
       <c r="G91" t="s">
         <v>1804</v>
       </c>
-      <c r="H91" t="e">
-        <f>VLOOKUP(D91,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H91" t="str">
+        <f>VLOOKUP(D91,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -8956,7 +8956,7 @@
         <v>1804</v>
       </c>
       <c r="H92" t="str">
-        <f>VLOOKUP(D92,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D92,name_map!$A$2:$C$33,3,0)</f>
         <v>BĐS KCN</v>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
         <v>1804</v>
       </c>
       <c r="H93" t="str">
-        <f>VLOOKUP(D93,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D93,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -9012,7 +9012,7 @@
         <v>1804</v>
       </c>
       <c r="H94" t="str">
-        <f>VLOOKUP(D94,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D94,name_map!$A$2:$C$33,3,0)</f>
         <v>Du lịch và DV</v>
       </c>
     </row>
@@ -9040,7 +9040,7 @@
         <v>1804</v>
       </c>
       <c r="H95" t="str">
-        <f>VLOOKUP(D95,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D95,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
         <v>1804</v>
       </c>
       <c r="H96" t="str">
-        <f>VLOOKUP(D96,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D96,name_map!$A$2:$C$33,3,0)</f>
         <v>Y tế</v>
       </c>
     </row>
@@ -9096,7 +9096,7 @@
         <v>1804</v>
       </c>
       <c r="H97" t="str">
-        <f>VLOOKUP(D97,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D97,name_map!$A$2:$C$33,3,0)</f>
         <v>Y tế</v>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
         <v>1804</v>
       </c>
       <c r="H98" t="str">
-        <f>VLOOKUP(D98,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D98,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -9152,7 +9152,7 @@
         <v>1804</v>
       </c>
       <c r="H99" t="str">
-        <f>VLOOKUP(D99,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D99,name_map!$A$2:$C$33,3,0)</f>
         <v>Y tế</v>
       </c>
     </row>
@@ -9180,7 +9180,7 @@
         <v>1822</v>
       </c>
       <c r="H100" t="str">
-        <f>VLOOKUP(D100,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D100,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
         <v>1804</v>
       </c>
       <c r="H101" t="str">
-        <f>VLOOKUP(D101,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D101,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
         <v>1804</v>
       </c>
       <c r="H102" t="str">
-        <f>VLOOKUP(D102,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D102,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -9264,7 +9264,7 @@
         <v>1822</v>
       </c>
       <c r="H103" t="str">
-        <f>VLOOKUP(D103,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D103,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -9292,7 +9292,7 @@
         <v>1804</v>
       </c>
       <c r="H104" t="str">
-        <f>VLOOKUP(D104,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D104,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -9319,9 +9319,9 @@
       <c r="G105" t="s">
         <v>1822</v>
       </c>
-      <c r="H105" t="e">
-        <f>VLOOKUP(D105,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H105" t="str">
+        <f>VLOOKUP(D105,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bán lẻ</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -9348,7 +9348,7 @@
         <v>1804</v>
       </c>
       <c r="H106" t="str">
-        <f>VLOOKUP(D106,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D106,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
         <v>1804</v>
       </c>
       <c r="H107" t="str">
-        <f>VLOOKUP(D107,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D107,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
         <v>1804</v>
       </c>
       <c r="H108" t="str">
-        <f>VLOOKUP(D108,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D108,name_map!$A$2:$C$33,3,0)</f>
         <v>Y tế</v>
       </c>
     </row>
@@ -9432,7 +9432,7 @@
         <v>1804</v>
       </c>
       <c r="H109" t="str">
-        <f>VLOOKUP(D109,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D109,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -9460,7 +9460,7 @@
         <v>1804</v>
       </c>
       <c r="H110" t="str">
-        <f>VLOOKUP(D110,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D110,name_map!$A$2:$C$33,3,0)</f>
         <v>Y tế</v>
       </c>
     </row>
@@ -9488,7 +9488,7 @@
         <v>1822</v>
       </c>
       <c r="H111" t="str">
-        <f>VLOOKUP(D111,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D111,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -9515,9 +9515,9 @@
       <c r="G112" t="s">
         <v>1804</v>
       </c>
-      <c r="H112" t="e">
-        <f>VLOOKUP(D112,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H112" t="str">
+        <f>VLOOKUP(D112,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -9544,7 +9544,7 @@
         <v>1804</v>
       </c>
       <c r="H113" t="str">
-        <f>VLOOKUP(D113,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D113,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -9571,9 +9571,9 @@
       <c r="G114" t="s">
         <v>1804</v>
       </c>
-      <c r="H114" t="e">
-        <f>VLOOKUP(D114,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H114" t="str">
+        <f>VLOOKUP(D114,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -9600,7 +9600,7 @@
         <v>1804</v>
       </c>
       <c r="H115" t="str">
-        <f>VLOOKUP(D115,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D115,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -9628,7 +9628,7 @@
         <v>1822</v>
       </c>
       <c r="H116" t="str">
-        <f>VLOOKUP(D116,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D116,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
         <v>1804</v>
       </c>
       <c r="H117" t="str">
-        <f>VLOOKUP(D117,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D117,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
         <v>1804</v>
       </c>
       <c r="H118" t="str">
-        <f>VLOOKUP(D118,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D118,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -9712,7 +9712,7 @@
         <v>1804</v>
       </c>
       <c r="H119" t="str">
-        <f>VLOOKUP(D119,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D119,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -9740,7 +9740,7 @@
         <v>1804</v>
       </c>
       <c r="H120" t="str">
-        <f>VLOOKUP(D120,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D120,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -9767,9 +9767,9 @@
       <c r="G121" t="s">
         <v>1822</v>
       </c>
-      <c r="H121" t="e">
-        <f>VLOOKUP(D121,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H121" t="str">
+        <f>VLOOKUP(D121,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -9796,7 +9796,7 @@
         <v>1804</v>
       </c>
       <c r="H122" t="str">
-        <f>VLOOKUP(D122,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D122,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
         <v>1804</v>
       </c>
       <c r="H123" t="str">
-        <f>VLOOKUP(D123,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D123,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -9852,7 +9852,7 @@
         <v>1804</v>
       </c>
       <c r="H124" t="str">
-        <f>VLOOKUP(D124,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D124,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -9879,9 +9879,9 @@
       <c r="G125" t="s">
         <v>1822</v>
       </c>
-      <c r="H125" t="e">
-        <f>VLOOKUP(D125,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H125" t="str">
+        <f>VLOOKUP(D125,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -9908,7 +9908,7 @@
         <v>1822</v>
       </c>
       <c r="H126" t="str">
-        <f>VLOOKUP(D126,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D126,name_map!$A$2:$C$33,3,0)</f>
         <v>BĐS KCN</v>
       </c>
     </row>
@@ -9936,7 +9936,7 @@
         <v>1804</v>
       </c>
       <c r="H127" t="str">
-        <f>VLOOKUP(D127,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D127,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -9963,9 +9963,9 @@
       <c r="G128" t="s">
         <v>1804</v>
       </c>
-      <c r="H128" t="e">
-        <f>VLOOKUP(D128,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H128" t="str">
+        <f>VLOOKUP(D128,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -9992,7 +9992,7 @@
         <v>1804</v>
       </c>
       <c r="H129" t="str">
-        <f>VLOOKUP(D129,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D129,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -10020,7 +10020,7 @@
         <v>1804</v>
       </c>
       <c r="H130" t="str">
-        <f>VLOOKUP(D130,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D130,name_map!$A$2:$C$33,3,0)</f>
         <v>Y tế</v>
       </c>
     </row>
@@ -10048,7 +10048,7 @@
         <v>1822</v>
       </c>
       <c r="H131" t="str">
-        <f>VLOOKUP(D131,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D131,name_map!$A$2:$C$33,3,0)</f>
         <v>Y tế</v>
       </c>
     </row>
@@ -10075,9 +10075,9 @@
       <c r="G132" t="s">
         <v>1822</v>
       </c>
-      <c r="H132" t="e">
-        <f>VLOOKUP(D132,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H132" t="str">
+        <f>VLOOKUP(D132,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -10104,7 +10104,7 @@
         <v>1822</v>
       </c>
       <c r="H133" t="str">
-        <f>VLOOKUP(D133,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D133,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -10131,9 +10131,9 @@
       <c r="G134" t="s">
         <v>1804</v>
       </c>
-      <c r="H134" t="e">
-        <f>VLOOKUP(D134,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H134" t="str">
+        <f>VLOOKUP(D134,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -10160,7 +10160,7 @@
         <v>1804</v>
       </c>
       <c r="H135" t="str">
-        <f>VLOOKUP(D135,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D135,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -10187,9 +10187,9 @@
       <c r="G136" t="s">
         <v>1822</v>
       </c>
-      <c r="H136" t="e">
-        <f>VLOOKUP(D136,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H136" t="str">
+        <f>VLOOKUP(D136,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -10216,7 +10216,7 @@
         <v>1822</v>
       </c>
       <c r="H137" t="str">
-        <f>VLOOKUP(D137,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D137,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghệ</v>
       </c>
     </row>
@@ -10244,7 +10244,7 @@
         <v>1804</v>
       </c>
       <c r="H138" t="str">
-        <f>VLOOKUP(D138,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D138,name_map!$A$2:$C$33,3,0)</f>
         <v>Dệt may</v>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
         <v>1822</v>
       </c>
       <c r="H139" t="str">
-        <f>VLOOKUP(D139,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D139,name_map!$A$2:$C$33,3,0)</f>
         <v>Công ty tài chính</v>
       </c>
     </row>
@@ -10300,7 +10300,7 @@
         <v>1822</v>
       </c>
       <c r="H140" t="str">
-        <f>VLOOKUP(D140,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D140,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -10328,7 +10328,7 @@
         <v>1804</v>
       </c>
       <c r="H141" t="str">
-        <f>VLOOKUP(D141,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D141,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -10356,7 +10356,7 @@
         <v>1804</v>
       </c>
       <c r="H142" t="str">
-        <f>VLOOKUP(D142,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D142,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -10384,7 +10384,7 @@
         <v>1804</v>
       </c>
       <c r="H143" t="str">
-        <f>VLOOKUP(D143,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D143,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
         <v>1822</v>
       </c>
       <c r="H144" t="str">
-        <f>VLOOKUP(D144,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D144,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -10439,9 +10439,9 @@
       <c r="G145" t="s">
         <v>1804</v>
       </c>
-      <c r="H145" t="e">
-        <f>VLOOKUP(D145,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H145" t="str">
+        <f>VLOOKUP(D145,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -10467,9 +10467,9 @@
       <c r="G146" t="s">
         <v>1804</v>
       </c>
-      <c r="H146" t="e">
-        <f>VLOOKUP(D146,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H146" t="str">
+        <f>VLOOKUP(D146,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -10496,7 +10496,7 @@
         <v>1804</v>
       </c>
       <c r="H147" t="str">
-        <f>VLOOKUP(D147,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D147,name_map!$A$2:$C$33,3,0)</f>
         <v>Thuỷ sản</v>
       </c>
     </row>
@@ -10524,7 +10524,7 @@
         <v>1804</v>
       </c>
       <c r="H148" t="str">
-        <f>VLOOKUP(D148,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D148,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghệ</v>
       </c>
     </row>
@@ -10551,9 +10551,9 @@
       <c r="G149" t="s">
         <v>1804</v>
       </c>
-      <c r="H149" t="e">
-        <f>VLOOKUP(D149,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H149" t="str">
+        <f>VLOOKUP(D149,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bán lẻ</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -10580,7 +10580,7 @@
         <v>1804</v>
       </c>
       <c r="H150" t="str">
-        <f>VLOOKUP(D150,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D150,name_map!$A$2:$C$33,3,0)</f>
         <v>Dệt may</v>
       </c>
     </row>
@@ -10608,7 +10608,7 @@
         <v>1804</v>
       </c>
       <c r="H151" t="str">
-        <f>VLOOKUP(D151,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D151,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -10636,7 +10636,7 @@
         <v>1804</v>
       </c>
       <c r="H152" t="str">
-        <f>VLOOKUP(D152,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D152,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
         <v>1804</v>
       </c>
       <c r="H153" t="str">
-        <f>VLOOKUP(D153,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D153,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
         <v>1804</v>
       </c>
       <c r="H154" t="str">
-        <f>VLOOKUP(D154,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D154,name_map!$A$2:$C$33,3,0)</f>
         <v>Thép</v>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
         <v>1804</v>
       </c>
       <c r="H155" t="str">
-        <f>VLOOKUP(D155,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D155,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -10748,7 +10748,7 @@
         <v>1804</v>
       </c>
       <c r="H156" t="str">
-        <f>VLOOKUP(D156,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D156,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -10776,7 +10776,7 @@
         <v>1804</v>
       </c>
       <c r="H157" t="str">
-        <f>VLOOKUP(D157,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D157,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
         <v>1804</v>
       </c>
       <c r="H158" t="str">
-        <f>VLOOKUP(D158,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D158,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -10832,7 +10832,7 @@
         <v>1822</v>
       </c>
       <c r="H159" t="str">
-        <f>VLOOKUP(D159,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D159,name_map!$A$2:$C$33,3,0)</f>
         <v>Dệt may</v>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
         <v>1804</v>
       </c>
       <c r="H160" t="str">
-        <f>VLOOKUP(D160,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D160,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -10888,7 +10888,7 @@
         <v>1804</v>
       </c>
       <c r="H161" t="str">
-        <f>VLOOKUP(D161,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D161,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -10916,7 +10916,7 @@
         <v>1804</v>
       </c>
       <c r="H162" t="str">
-        <f>VLOOKUP(D162,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D162,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -10944,7 +10944,7 @@
         <v>1804</v>
       </c>
       <c r="H163" t="str">
-        <f>VLOOKUP(D163,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D163,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -10972,7 +10972,7 @@
         <v>1822</v>
       </c>
       <c r="H164" t="str">
-        <f>VLOOKUP(D164,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D164,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -11000,7 +11000,7 @@
         <v>1822</v>
       </c>
       <c r="H165" t="str">
-        <f>VLOOKUP(D165,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D165,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
         <v>1804</v>
       </c>
       <c r="H166" t="str">
-        <f>VLOOKUP(D166,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D166,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
         <v>1822</v>
       </c>
       <c r="H167" t="str">
-        <f>VLOOKUP(D167,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D167,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -11083,9 +11083,9 @@
       <c r="G168" t="s">
         <v>1804</v>
       </c>
-      <c r="H168" t="e">
-        <f>VLOOKUP(D168,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H168" t="str">
+        <f>VLOOKUP(D168,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -11112,7 +11112,7 @@
         <v>1804</v>
       </c>
       <c r="H169" t="str">
-        <f>VLOOKUP(D169,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D169,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -11140,7 +11140,7 @@
         <v>1804</v>
       </c>
       <c r="H170" t="str">
-        <f>VLOOKUP(D170,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D170,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -11168,7 +11168,7 @@
         <v>1822</v>
       </c>
       <c r="H171" t="str">
-        <f>VLOOKUP(D171,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D171,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -11196,7 +11196,7 @@
         <v>1804</v>
       </c>
       <c r="H172" t="str">
-        <f>VLOOKUP(D172,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D172,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -11224,7 +11224,7 @@
         <v>1822</v>
       </c>
       <c r="H173" t="str">
-        <f>VLOOKUP(D173,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D173,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -11251,9 +11251,9 @@
       <c r="G174" t="s">
         <v>1804</v>
       </c>
-      <c r="H174" t="e">
-        <f>VLOOKUP(D174,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H174" t="str">
+        <f>VLOOKUP(D174,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -11280,7 +11280,7 @@
         <v>1804</v>
       </c>
       <c r="H175" t="str">
-        <f>VLOOKUP(D175,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D175,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -11308,7 +11308,7 @@
         <v>1804</v>
       </c>
       <c r="H176" t="str">
-        <f>VLOOKUP(D176,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D176,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -11335,9 +11335,9 @@
       <c r="G177" t="s">
         <v>1822</v>
       </c>
-      <c r="H177" t="e">
-        <f>VLOOKUP(D177,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H177" t="str">
+        <f>VLOOKUP(D177,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -11363,9 +11363,9 @@
       <c r="G178" t="s">
         <v>1804</v>
       </c>
-      <c r="H178" t="e">
-        <f>VLOOKUP(D178,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H178" t="str">
+        <f>VLOOKUP(D178,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -11392,7 +11392,7 @@
         <v>1822</v>
       </c>
       <c r="H179" t="str">
-        <f>VLOOKUP(D179,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D179,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -11420,7 +11420,7 @@
         <v>1804</v>
       </c>
       <c r="H180" t="str">
-        <f>VLOOKUP(D180,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D180,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -11447,9 +11447,9 @@
       <c r="G181" t="s">
         <v>1822</v>
       </c>
-      <c r="H181" t="e">
-        <f>VLOOKUP(D181,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H181" t="str">
+        <f>VLOOKUP(D181,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -11476,7 +11476,7 @@
         <v>1804</v>
       </c>
       <c r="H182" t="str">
-        <f>VLOOKUP(D182,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D182,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
         <v>1804</v>
       </c>
       <c r="H183" t="str">
-        <f>VLOOKUP(D183,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D183,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -11532,7 +11532,7 @@
         <v>1804</v>
       </c>
       <c r="H184" t="str">
-        <f>VLOOKUP(D184,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D184,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -11559,9 +11559,9 @@
       <c r="G185" t="s">
         <v>1804</v>
       </c>
-      <c r="H185" t="e">
-        <f>VLOOKUP(D185,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H185" t="str">
+        <f>VLOOKUP(D185,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -11588,7 +11588,7 @@
         <v>1804</v>
       </c>
       <c r="H186" t="str">
-        <f>VLOOKUP(D186,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D186,name_map!$A$2:$C$33,3,0)</f>
         <v>Thép</v>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
         <v>1804</v>
       </c>
       <c r="H187" t="str">
-        <f>VLOOKUP(D187,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D187,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -11644,7 +11644,7 @@
         <v>1804</v>
       </c>
       <c r="H188" t="str">
-        <f>VLOOKUP(D188,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D188,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -11672,7 +11672,7 @@
         <v>1822</v>
       </c>
       <c r="H189" t="str">
-        <f>VLOOKUP(D189,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D189,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -11700,7 +11700,7 @@
         <v>1804</v>
       </c>
       <c r="H190" t="str">
-        <f>VLOOKUP(D190,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D190,name_map!$A$2:$C$33,3,0)</f>
         <v>Thép</v>
       </c>
     </row>
@@ -11727,9 +11727,9 @@
       <c r="G191" t="s">
         <v>1804</v>
       </c>
-      <c r="H191" t="e">
-        <f>VLOOKUP(D191,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H191" t="str">
+        <f>VLOOKUP(D191,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
@@ -11755,9 +11755,9 @@
       <c r="G192" t="s">
         <v>1804</v>
       </c>
-      <c r="H192" t="e">
-        <f>VLOOKUP(D192,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H192" t="str">
+        <f>VLOOKUP(D192,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
@@ -11784,7 +11784,7 @@
         <v>1822</v>
       </c>
       <c r="H193" t="str">
-        <f>VLOOKUP(D193,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D193,name_map!$A$2:$C$33,3,0)</f>
         <v>Thép</v>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
         <v>1822</v>
       </c>
       <c r="H194" t="str">
-        <f>VLOOKUP(D194,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D194,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -11840,7 +11840,7 @@
         <v>1804</v>
       </c>
       <c r="H195" t="str">
-        <f>VLOOKUP(D195,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D195,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -11868,7 +11868,7 @@
         <v>1804</v>
       </c>
       <c r="H196" t="str">
-        <f>VLOOKUP(D196,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D196,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -11896,7 +11896,7 @@
         <v>1804</v>
       </c>
       <c r="H197" t="str">
-        <f>VLOOKUP(D197,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D197,name_map!$A$2:$C$33,3,0)</f>
         <v>Dệt may</v>
       </c>
     </row>
@@ -11924,7 +11924,7 @@
         <v>1804</v>
       </c>
       <c r="H198" t="str">
-        <f>VLOOKUP(D198,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D198,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -11952,7 +11952,7 @@
         <v>1804</v>
       </c>
       <c r="H199" t="str">
-        <f>VLOOKUP(D199,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D199,name_map!$A$2:$C$33,3,0)</f>
         <v>Du lịch và DV</v>
       </c>
     </row>
@@ -11980,7 +11980,7 @@
         <v>1822</v>
       </c>
       <c r="H200" t="str">
-        <f>VLOOKUP(D200,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D200,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -12008,7 +12008,7 @@
         <v>1804</v>
       </c>
       <c r="H201" t="str">
-        <f>VLOOKUP(D201,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D201,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
         <v>1822</v>
       </c>
       <c r="H202" t="str">
-        <f>VLOOKUP(D202,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D202,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -12064,7 +12064,7 @@
         <v>1822</v>
       </c>
       <c r="H203" t="str">
-        <f>VLOOKUP(D203,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D203,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -12092,7 +12092,7 @@
         <v>1804</v>
       </c>
       <c r="H204" t="str">
-        <f>VLOOKUP(D204,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D204,name_map!$A$2:$C$33,3,0)</f>
         <v>Du lịch và DV</v>
       </c>
     </row>
@@ -12120,7 +12120,7 @@
         <v>1804</v>
       </c>
       <c r="H205" t="str">
-        <f>VLOOKUP(D205,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D205,name_map!$A$2:$C$33,3,0)</f>
         <v>Công ty tài chính</v>
       </c>
     </row>
@@ -12148,7 +12148,7 @@
         <v>1804</v>
       </c>
       <c r="H206" t="str">
-        <f>VLOOKUP(D206,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D206,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghệ</v>
       </c>
     </row>
@@ -12176,7 +12176,7 @@
         <v>1804</v>
       </c>
       <c r="H207" t="str">
-        <f>VLOOKUP(D207,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D207,name_map!$A$2:$C$33,3,0)</f>
         <v>BĐS KCN</v>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
         <v>1822</v>
       </c>
       <c r="H208" t="str">
-        <f>VLOOKUP(D208,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D208,name_map!$A$2:$C$33,3,0)</f>
         <v>Thuỷ sản</v>
       </c>
     </row>
@@ -12231,9 +12231,9 @@
       <c r="G209" t="s">
         <v>1804</v>
       </c>
-      <c r="H209" t="e">
-        <f>VLOOKUP(D209,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H209" t="str">
+        <f>VLOOKUP(D209,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
@@ -12259,9 +12259,9 @@
       <c r="G210" t="s">
         <v>1822</v>
       </c>
-      <c r="H210" t="e">
-        <f>VLOOKUP(D210,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H210" t="str">
+        <f>VLOOKUP(D210,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -12288,7 +12288,7 @@
         <v>1804</v>
       </c>
       <c r="H211" t="str">
-        <f>VLOOKUP(D211,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D211,name_map!$A$2:$C$33,3,0)</f>
         <v>Công ty tài chính</v>
       </c>
     </row>
@@ -12315,9 +12315,9 @@
       <c r="G212" t="s">
         <v>1822</v>
       </c>
-      <c r="H212" t="e">
-        <f>VLOOKUP(D212,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H212" t="str">
+        <f>VLOOKUP(D212,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -12343,9 +12343,9 @@
       <c r="G213" t="s">
         <v>1804</v>
       </c>
-      <c r="H213" t="e">
-        <f>VLOOKUP(D213,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H213" t="str">
+        <f>VLOOKUP(D213,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
@@ -12372,7 +12372,7 @@
         <v>1804</v>
       </c>
       <c r="H214" t="str">
-        <f>VLOOKUP(D214,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D214,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghệ</v>
       </c>
     </row>
@@ -12400,7 +12400,7 @@
         <v>1804</v>
       </c>
       <c r="H215" t="str">
-        <f>VLOOKUP(D215,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D215,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
         <v>1804</v>
       </c>
       <c r="H216" t="str">
-        <f>VLOOKUP(D216,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D216,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
         <v>1804</v>
       </c>
       <c r="H217" t="str">
-        <f>VLOOKUP(D217,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D217,name_map!$A$2:$C$33,3,0)</f>
         <v>Y tế</v>
       </c>
     </row>
@@ -12484,7 +12484,7 @@
         <v>1804</v>
       </c>
       <c r="H218" t="str">
-        <f>VLOOKUP(D218,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D218,name_map!$A$2:$C$33,3,0)</f>
         <v>BĐS KCN</v>
       </c>
     </row>
@@ -12512,7 +12512,7 @@
         <v>1804</v>
       </c>
       <c r="H219" t="str">
-        <f>VLOOKUP(D219,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D219,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -12539,9 +12539,9 @@
       <c r="G220" t="s">
         <v>1804</v>
       </c>
-      <c r="H220" t="e">
-        <f>VLOOKUP(D220,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H220" t="str">
+        <f>VLOOKUP(D220,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
@@ -12568,7 +12568,7 @@
         <v>1804</v>
       </c>
       <c r="H221" t="str">
-        <f>VLOOKUP(D221,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D221,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -12595,9 +12595,9 @@
       <c r="G222" t="s">
         <v>1804</v>
       </c>
-      <c r="H222" t="e">
-        <f>VLOOKUP(D222,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H222" t="str">
+        <f>VLOOKUP(D222,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
@@ -12624,7 +12624,7 @@
         <v>1804</v>
       </c>
       <c r="H223" t="str">
-        <f>VLOOKUP(D223,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D223,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -12652,7 +12652,7 @@
         <v>1804</v>
       </c>
       <c r="H224" t="str">
-        <f>VLOOKUP(D224,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D224,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -12680,7 +12680,7 @@
         <v>1804</v>
       </c>
       <c r="H225" t="str">
-        <f>VLOOKUP(D225,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D225,name_map!$A$2:$C$33,3,0)</f>
         <v>Dệt may</v>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
         <v>1804</v>
       </c>
       <c r="H226" t="str">
-        <f>VLOOKUP(D226,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D226,name_map!$A$2:$C$33,3,0)</f>
         <v>BĐS KCN</v>
       </c>
     </row>
@@ -12736,7 +12736,7 @@
         <v>1804</v>
       </c>
       <c r="H227" t="str">
-        <f>VLOOKUP(D227,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D227,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
         <v>1804</v>
       </c>
       <c r="H228" t="str">
-        <f>VLOOKUP(D228,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D228,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -12791,9 +12791,9 @@
       <c r="G229" t="s">
         <v>1804</v>
       </c>
-      <c r="H229" t="e">
-        <f>VLOOKUP(D229,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H229" t="str">
+        <f>VLOOKUP(D229,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
@@ -12820,7 +12820,7 @@
         <v>1822</v>
       </c>
       <c r="H230" t="str">
-        <f>VLOOKUP(D230,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D230,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -12848,7 +12848,7 @@
         <v>1804</v>
       </c>
       <c r="H231" t="str">
-        <f>VLOOKUP(D231,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D231,name_map!$A$2:$C$33,3,0)</f>
         <v>Thép</v>
       </c>
     </row>
@@ -12876,7 +12876,7 @@
         <v>1804</v>
       </c>
       <c r="H232" t="str">
-        <f>VLOOKUP(D232,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D232,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -12904,7 +12904,7 @@
         <v>1804</v>
       </c>
       <c r="H233" t="str">
-        <f>VLOOKUP(D233,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D233,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
         <v>1822</v>
       </c>
       <c r="H234" t="str">
-        <f>VLOOKUP(D234,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D234,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -12960,7 +12960,7 @@
         <v>1804</v>
       </c>
       <c r="H235" t="str">
-        <f>VLOOKUP(D235,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D235,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -12988,7 +12988,7 @@
         <v>1822</v>
       </c>
       <c r="H236" t="str">
-        <f>VLOOKUP(D236,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D236,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -13015,9 +13015,9 @@
       <c r="G237" t="s">
         <v>1804</v>
       </c>
-      <c r="H237" t="e">
-        <f>VLOOKUP(D237,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H237" t="str">
+        <f>VLOOKUP(D237,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
@@ -13044,7 +13044,7 @@
         <v>1804</v>
       </c>
       <c r="H238" t="str">
-        <f>VLOOKUP(D238,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D238,name_map!$A$2:$C$33,3,0)</f>
         <v>Y tế</v>
       </c>
     </row>
@@ -13071,9 +13071,9 @@
       <c r="G239" t="s">
         <v>1804</v>
       </c>
-      <c r="H239" t="e">
-        <f>VLOOKUP(D239,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H239" t="str">
+        <f>VLOOKUP(D239,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
@@ -13100,7 +13100,7 @@
         <v>1804</v>
       </c>
       <c r="H240" t="str">
-        <f>VLOOKUP(D240,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D240,name_map!$A$2:$C$33,3,0)</f>
         <v>BĐS KCN</v>
       </c>
     </row>
@@ -13128,7 +13128,7 @@
         <v>1822</v>
       </c>
       <c r="H241" t="str">
-        <f>VLOOKUP(D241,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D241,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -13155,9 +13155,9 @@
       <c r="G242" t="s">
         <v>1804</v>
       </c>
-      <c r="H242" t="e">
-        <f>VLOOKUP(D242,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H242" t="str">
+        <f>VLOOKUP(D242,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bán lẻ</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
@@ -13184,7 +13184,7 @@
         <v>1804</v>
       </c>
       <c r="H243" t="str">
-        <f>VLOOKUP(D243,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D243,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -13212,7 +13212,7 @@
         <v>1804</v>
       </c>
       <c r="H244" t="str">
-        <f>VLOOKUP(D244,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D244,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -13240,7 +13240,7 @@
         <v>1804</v>
       </c>
       <c r="H245" t="str">
-        <f>VLOOKUP(D245,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D245,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -13268,7 +13268,7 @@
         <v>1822</v>
       </c>
       <c r="H246" t="str">
-        <f>VLOOKUP(D246,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D246,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
         <v>1804</v>
       </c>
       <c r="H247" t="str">
-        <f>VLOOKUP(D247,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D247,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -13324,7 +13324,7 @@
         <v>1804</v>
       </c>
       <c r="H248" t="str">
-        <f>VLOOKUP(D248,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D248,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
         <v>1822</v>
       </c>
       <c r="H249" t="str">
-        <f>VLOOKUP(D249,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D249,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -13380,7 +13380,7 @@
         <v>1804</v>
       </c>
       <c r="H250" t="str">
-        <f>VLOOKUP(D250,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D250,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -13408,7 +13408,7 @@
         <v>1822</v>
       </c>
       <c r="H251" t="str">
-        <f>VLOOKUP(D251,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D251,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -13436,7 +13436,7 @@
         <v>1804</v>
       </c>
       <c r="H252" t="str">
-        <f>VLOOKUP(D252,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D252,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -13464,7 +13464,7 @@
         <v>1804</v>
       </c>
       <c r="H253" t="str">
-        <f>VLOOKUP(D253,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D253,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -13492,7 +13492,7 @@
         <v>1804</v>
       </c>
       <c r="H254" t="str">
-        <f>VLOOKUP(D254,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D254,name_map!$A$2:$C$33,3,0)</f>
         <v>Bảo hiểm</v>
       </c>
     </row>
@@ -13520,7 +13520,7 @@
         <v>1804</v>
       </c>
       <c r="H255" t="str">
-        <f>VLOOKUP(D255,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D255,name_map!$A$2:$C$33,3,0)</f>
         <v>Thuỷ sản</v>
       </c>
     </row>
@@ -13548,7 +13548,7 @@
         <v>1804</v>
       </c>
       <c r="H256" t="str">
-        <f>VLOOKUP(D256,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D256,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -13576,7 +13576,7 @@
         <v>1822</v>
       </c>
       <c r="H257" t="str">
-        <f>VLOOKUP(D257,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D257,name_map!$A$2:$C$33,3,0)</f>
         <v>Dệt may</v>
       </c>
     </row>
@@ -13604,7 +13604,7 @@
         <v>1804</v>
       </c>
       <c r="H258" t="str">
-        <f>VLOOKUP(D258,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D258,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -13632,7 +13632,7 @@
         <v>1804</v>
       </c>
       <c r="H259" t="str">
-        <f>VLOOKUP(D259,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D259,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -13660,7 +13660,7 @@
         <v>1822</v>
       </c>
       <c r="H260" t="str">
-        <f>VLOOKUP(D260,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D260,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -13688,7 +13688,7 @@
         <v>1804</v>
       </c>
       <c r="H261" t="str">
-        <f>VLOOKUP(D261,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D261,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -13715,9 +13715,9 @@
       <c r="G262" t="s">
         <v>1804</v>
       </c>
-      <c r="H262" t="e">
-        <f>VLOOKUP(D262,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H262" t="str">
+        <f>VLOOKUP(D262,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bán lẻ</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
@@ -13744,7 +13744,7 @@
         <v>1804</v>
       </c>
       <c r="H263" t="str">
-        <f>VLOOKUP(D263,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D263,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -13772,7 +13772,7 @@
         <v>1804</v>
       </c>
       <c r="H264" t="str">
-        <f>VLOOKUP(D264,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D264,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -13800,7 +13800,7 @@
         <v>1804</v>
       </c>
       <c r="H265" t="str">
-        <f>VLOOKUP(D265,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D265,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -13827,9 +13827,9 @@
       <c r="G266" t="s">
         <v>1804</v>
       </c>
-      <c r="H266" t="e">
-        <f>VLOOKUP(D266,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H266" t="str">
+        <f>VLOOKUP(D266,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
@@ -13856,7 +13856,7 @@
         <v>1804</v>
       </c>
       <c r="H267" t="str">
-        <f>VLOOKUP(D267,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D267,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -13883,9 +13883,9 @@
       <c r="G268" t="s">
         <v>1804</v>
       </c>
-      <c r="H268" t="e">
-        <f>VLOOKUP(D268,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H268" t="str">
+        <f>VLOOKUP(D268,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
@@ -13912,7 +13912,7 @@
         <v>1804</v>
       </c>
       <c r="H269" t="str">
-        <f>VLOOKUP(D269,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D269,name_map!$A$2:$C$33,3,0)</f>
         <v>Dệt may</v>
       </c>
     </row>
@@ -13940,7 +13940,7 @@
         <v>1804</v>
       </c>
       <c r="H270" t="str">
-        <f>VLOOKUP(D270,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D270,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -13968,7 +13968,7 @@
         <v>1804</v>
       </c>
       <c r="H271" t="str">
-        <f>VLOOKUP(D271,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D271,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -13980,10 +13980,10 @@
         <v>1795</v>
       </c>
       <c r="C272" t="s">
-        <v>1187</v>
+        <v>552</v>
       </c>
       <c r="D272" t="s">
-        <v>1187</v>
+        <v>552</v>
       </c>
       <c r="E272" t="str">
         <f>VLOOKUP(D272,name_map!$A$2:$D$24,2,0)</f>
@@ -13996,8 +13996,8 @@
         <v>1822</v>
       </c>
       <c r="H272" t="str">
-        <f>VLOOKUP(D272,name_map!$A$4:$C$24,3,0)</f>
-        <v>Xây dựng</v>
+        <f>VLOOKUP(D272,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
@@ -14024,7 +14024,7 @@
         <v>1804</v>
       </c>
       <c r="H273" t="str">
-        <f>VLOOKUP(D273,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D273,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
         <v>1822</v>
       </c>
       <c r="H274" t="str">
-        <f>VLOOKUP(D274,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D274,name_map!$A$2:$C$33,3,0)</f>
         <v>Thép</v>
       </c>
     </row>
@@ -14079,9 +14079,9 @@
       <c r="G275" t="s">
         <v>1804</v>
       </c>
-      <c r="H275" t="e">
-        <f>VLOOKUP(D275,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H275" t="str">
+        <f>VLOOKUP(D275,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
@@ -14107,9 +14107,9 @@
       <c r="G276" t="s">
         <v>1804</v>
       </c>
-      <c r="H276" t="e">
-        <f>VLOOKUP(D276,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H276" t="str">
+        <f>VLOOKUP(D276,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
@@ -14136,7 +14136,7 @@
         <v>1822</v>
       </c>
       <c r="H277" t="str">
-        <f>VLOOKUP(D277,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D277,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -14164,7 +14164,7 @@
         <v>1804</v>
       </c>
       <c r="H278" t="str">
-        <f>VLOOKUP(D278,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D278,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -14192,7 +14192,7 @@
         <v>1804</v>
       </c>
       <c r="H279" t="str">
-        <f>VLOOKUP(D279,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D279,name_map!$A$2:$C$33,3,0)</f>
         <v>BĐS KCN</v>
       </c>
     </row>
@@ -14220,7 +14220,7 @@
         <v>1804</v>
       </c>
       <c r="H280" t="str">
-        <f>VLOOKUP(D280,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D280,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -14248,7 +14248,7 @@
         <v>1804</v>
       </c>
       <c r="H281" t="str">
-        <f>VLOOKUP(D281,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D281,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -14275,9 +14275,9 @@
       <c r="G282" t="s">
         <v>1804</v>
       </c>
-      <c r="H282" t="e">
-        <f>VLOOKUP(D282,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H282" t="str">
+        <f>VLOOKUP(D282,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
@@ -14304,7 +14304,7 @@
         <v>1804</v>
       </c>
       <c r="H283" t="str">
-        <f>VLOOKUP(D283,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D283,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -14332,7 +14332,7 @@
         <v>1804</v>
       </c>
       <c r="H284" t="str">
-        <f>VLOOKUP(D284,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D284,name_map!$A$2:$C$33,3,0)</f>
         <v>Du lịch và DV</v>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>1804</v>
       </c>
       <c r="H285" t="str">
-        <f>VLOOKUP(D285,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D285,name_map!$A$2:$C$33,3,0)</f>
         <v>Du lịch và DV</v>
       </c>
     </row>
@@ -14387,9 +14387,9 @@
       <c r="G286" t="s">
         <v>1822</v>
       </c>
-      <c r="H286" t="e">
-        <f>VLOOKUP(D286,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H286" t="str">
+        <f>VLOOKUP(D286,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
@@ -14416,7 +14416,7 @@
         <v>1822</v>
       </c>
       <c r="H287" t="str">
-        <f>VLOOKUP(D287,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D287,name_map!$A$2:$C$33,3,0)</f>
         <v>Dầu khí</v>
       </c>
     </row>
@@ -14444,7 +14444,7 @@
         <v>1822</v>
       </c>
       <c r="H288" t="str">
-        <f>VLOOKUP(D288,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D288,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -14472,7 +14472,7 @@
         <v>1804</v>
       </c>
       <c r="H289" t="str">
-        <f>VLOOKUP(D289,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D289,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
         <v>1804</v>
       </c>
       <c r="H290" t="str">
-        <f>VLOOKUP(D290,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D290,name_map!$A$2:$C$33,3,0)</f>
         <v>Thép</v>
       </c>
     </row>
@@ -14528,7 +14528,7 @@
         <v>1804</v>
       </c>
       <c r="H291" t="str">
-        <f>VLOOKUP(D291,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D291,name_map!$A$2:$C$33,3,0)</f>
         <v>Y tế</v>
       </c>
     </row>
@@ -14556,7 +14556,7 @@
         <v>1804</v>
       </c>
       <c r="H292" t="str">
-        <f>VLOOKUP(D292,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D292,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -14584,7 +14584,7 @@
         <v>1804</v>
       </c>
       <c r="H293" t="str">
-        <f>VLOOKUP(D293,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D293,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -14612,7 +14612,7 @@
         <v>1804</v>
       </c>
       <c r="H294" t="str">
-        <f>VLOOKUP(D294,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D294,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -14640,7 +14640,7 @@
         <v>1804</v>
       </c>
       <c r="H295" t="str">
-        <f>VLOOKUP(D295,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D295,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -14667,9 +14667,9 @@
       <c r="G296" t="s">
         <v>1804</v>
       </c>
-      <c r="H296" t="e">
-        <f>VLOOKUP(D296,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H296" t="str">
+        <f>VLOOKUP(D296,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
@@ -14695,9 +14695,9 @@
       <c r="G297" t="s">
         <v>1822</v>
       </c>
-      <c r="H297" t="e">
-        <f>VLOOKUP(D297,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H297" t="str">
+        <f>VLOOKUP(D297,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bán lẻ</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
@@ -14723,9 +14723,9 @@
       <c r="G298" t="s">
         <v>1822</v>
       </c>
-      <c r="H298" t="e">
-        <f>VLOOKUP(D298,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H298" t="str">
+        <f>VLOOKUP(D298,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
@@ -14752,7 +14752,7 @@
         <v>1804</v>
       </c>
       <c r="H299" t="str">
-        <f>VLOOKUP(D299,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D299,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -14780,7 +14780,7 @@
         <v>1804</v>
       </c>
       <c r="H300" t="str">
-        <f>VLOOKUP(D300,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D300,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -14808,7 +14808,7 @@
         <v>1804</v>
       </c>
       <c r="H301" t="str">
-        <f>VLOOKUP(D301,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D301,name_map!$A$2:$C$33,3,0)</f>
         <v>Bảo hiểm</v>
       </c>
     </row>
@@ -14836,7 +14836,7 @@
         <v>1804</v>
       </c>
       <c r="H302" t="str">
-        <f>VLOOKUP(D302,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D302,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -14864,7 +14864,7 @@
         <v>1804</v>
       </c>
       <c r="H303" t="str">
-        <f>VLOOKUP(D303,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D303,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -14892,7 +14892,7 @@
         <v>1804</v>
       </c>
       <c r="H304" t="str">
-        <f>VLOOKUP(D304,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D304,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -14920,7 +14920,7 @@
         <v>1822</v>
       </c>
       <c r="H305" t="str">
-        <f>VLOOKUP(D305,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D305,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -14948,7 +14948,7 @@
         <v>1804</v>
       </c>
       <c r="H306" t="str">
-        <f>VLOOKUP(D306,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D306,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -14976,7 +14976,7 @@
         <v>1804</v>
       </c>
       <c r="H307" t="str">
-        <f>VLOOKUP(D307,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D307,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
         <v>1804</v>
       </c>
       <c r="H308" t="str">
-        <f>VLOOKUP(D308,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D308,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -15032,7 +15032,7 @@
         <v>1804</v>
       </c>
       <c r="H309" t="str">
-        <f>VLOOKUP(D309,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D309,name_map!$A$2:$C$33,3,0)</f>
         <v>Dầu khí</v>
       </c>
     </row>
@@ -15060,7 +15060,7 @@
         <v>1804</v>
       </c>
       <c r="H310" t="str">
-        <f>VLOOKUP(D310,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D310,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
         <v>1804</v>
       </c>
       <c r="H311" t="str">
-        <f>VLOOKUP(D311,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D311,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -15116,7 +15116,7 @@
         <v>1822</v>
       </c>
       <c r="H312" t="str">
-        <f>VLOOKUP(D312,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D312,name_map!$A$2:$C$33,3,0)</f>
         <v>Thép</v>
       </c>
     </row>
@@ -15144,7 +15144,7 @@
         <v>1804</v>
       </c>
       <c r="H313" t="str">
-        <f>VLOOKUP(D313,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D313,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -15172,7 +15172,7 @@
         <v>1804</v>
       </c>
       <c r="H314" t="str">
-        <f>VLOOKUP(D314,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D314,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -15200,7 +15200,7 @@
         <v>1804</v>
       </c>
       <c r="H315" t="str">
-        <f>VLOOKUP(D315,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D315,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -15228,7 +15228,7 @@
         <v>1804</v>
       </c>
       <c r="H316" t="str">
-        <f>VLOOKUP(D316,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D316,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -15255,9 +15255,9 @@
       <c r="G317" t="s">
         <v>1804</v>
       </c>
-      <c r="H317" t="e">
-        <f>VLOOKUP(D317,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H317" t="str">
+        <f>VLOOKUP(D317,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bán lẻ</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
@@ -15284,7 +15284,7 @@
         <v>1804</v>
       </c>
       <c r="H318" t="str">
-        <f>VLOOKUP(D318,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D318,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -15312,7 +15312,7 @@
         <v>1804</v>
       </c>
       <c r="H319" t="str">
-        <f>VLOOKUP(D319,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D319,name_map!$A$2:$C$33,3,0)</f>
         <v>Dầu khí</v>
       </c>
     </row>
@@ -15340,7 +15340,7 @@
         <v>1822</v>
       </c>
       <c r="H320" t="str">
-        <f>VLOOKUP(D320,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D320,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -15368,7 +15368,7 @@
         <v>1804</v>
       </c>
       <c r="H321" t="str">
-        <f>VLOOKUP(D321,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D321,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -15396,7 +15396,7 @@
         <v>1804</v>
       </c>
       <c r="H322" t="str">
-        <f>VLOOKUP(D322,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D322,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -15423,9 +15423,9 @@
       <c r="G323" t="s">
         <v>1804</v>
       </c>
-      <c r="H323" t="e">
-        <f>VLOOKUP(D323,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H323" t="str">
+        <f>VLOOKUP(D323,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
@@ -15452,7 +15452,7 @@
         <v>1804</v>
       </c>
       <c r="H324" t="str">
-        <f>VLOOKUP(D324,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D324,name_map!$A$2:$C$33,3,0)</f>
         <v>Dầu khí</v>
       </c>
     </row>
@@ -15479,9 +15479,9 @@
       <c r="G325" t="s">
         <v>1822</v>
       </c>
-      <c r="H325" t="e">
-        <f>VLOOKUP(D325,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H325" t="str">
+        <f>VLOOKUP(D325,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
@@ -15508,7 +15508,7 @@
         <v>1804</v>
       </c>
       <c r="H326" t="str">
-        <f>VLOOKUP(D326,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D326,name_map!$A$2:$C$33,3,0)</f>
         <v>Dầu khí</v>
       </c>
     </row>
@@ -15536,7 +15536,7 @@
         <v>1822</v>
       </c>
       <c r="H327" t="str">
-        <f>VLOOKUP(D327,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D327,name_map!$A$2:$C$33,3,0)</f>
         <v>Dầu khí</v>
       </c>
     </row>
@@ -15564,7 +15564,7 @@
         <v>1822</v>
       </c>
       <c r="H328" t="str">
-        <f>VLOOKUP(D328,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D328,name_map!$A$2:$C$33,3,0)</f>
         <v>Dầu khí</v>
       </c>
     </row>
@@ -15592,7 +15592,7 @@
         <v>1804</v>
       </c>
       <c r="H329" t="str">
-        <f>VLOOKUP(D329,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D329,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -15620,7 +15620,7 @@
         <v>1804</v>
       </c>
       <c r="H330" t="str">
-        <f>VLOOKUP(D330,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D330,name_map!$A$2:$C$33,3,0)</f>
         <v>Bảo hiểm</v>
       </c>
     </row>
@@ -15647,9 +15647,9 @@
       <c r="G331" t="s">
         <v>1804</v>
       </c>
-      <c r="H331" t="e">
-        <f>VLOOKUP(D331,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H331" t="str">
+        <f>VLOOKUP(D331,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
@@ -15676,7 +15676,7 @@
         <v>1804</v>
       </c>
       <c r="H332" t="str">
-        <f>VLOOKUP(D332,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D332,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -15704,7 +15704,7 @@
         <v>1822</v>
       </c>
       <c r="H333" t="str">
-        <f>VLOOKUP(D333,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D333,name_map!$A$2:$C$33,3,0)</f>
         <v>Dầu khí</v>
       </c>
     </row>
@@ -15732,7 +15732,7 @@
         <v>1822</v>
       </c>
       <c r="H334" t="str">
-        <f>VLOOKUP(D334,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D334,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -15760,7 +15760,7 @@
         <v>1822</v>
       </c>
       <c r="H335" t="str">
-        <f>VLOOKUP(D335,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D335,name_map!$A$2:$C$33,3,0)</f>
         <v>Dầu khí</v>
       </c>
     </row>
@@ -15788,7 +15788,7 @@
         <v>1804</v>
       </c>
       <c r="H336" t="str">
-        <f>VLOOKUP(D336,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D336,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -15815,9 +15815,9 @@
       <c r="G337" t="s">
         <v>1822</v>
       </c>
-      <c r="H337" t="e">
-        <f>VLOOKUP(D337,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H337" t="str">
+        <f>VLOOKUP(D337,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
@@ -15844,7 +15844,7 @@
         <v>1822</v>
       </c>
       <c r="H338" t="str">
-        <f>VLOOKUP(D338,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D338,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -15871,9 +15871,9 @@
       <c r="G339" t="s">
         <v>1804</v>
       </c>
-      <c r="H339" t="e">
-        <f>VLOOKUP(D339,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H339" t="str">
+        <f>VLOOKUP(D339,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
@@ -15900,7 +15900,7 @@
         <v>1804</v>
       </c>
       <c r="H340" t="str">
-        <f>VLOOKUP(D340,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D340,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -15928,7 +15928,7 @@
         <v>1804</v>
       </c>
       <c r="H341" t="str">
-        <f>VLOOKUP(D341,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D341,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -15956,7 +15956,7 @@
         <v>1804</v>
       </c>
       <c r="H342" t="str">
-        <f>VLOOKUP(D342,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D342,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -15983,9 +15983,9 @@
       <c r="G343" t="s">
         <v>1804</v>
       </c>
-      <c r="H343" t="e">
-        <f>VLOOKUP(D343,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H343" t="str">
+        <f>VLOOKUP(D343,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
@@ -16012,7 +16012,7 @@
         <v>1804</v>
       </c>
       <c r="H344" t="str">
-        <f>VLOOKUP(D344,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D344,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -16040,7 +16040,7 @@
         <v>1804</v>
       </c>
       <c r="H345" t="str">
-        <f>VLOOKUP(D345,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D345,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -16068,7 +16068,7 @@
         <v>1804</v>
       </c>
       <c r="H346" t="str">
-        <f>VLOOKUP(D346,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D346,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -16096,7 +16096,7 @@
         <v>1804</v>
       </c>
       <c r="H347" t="str">
-        <f>VLOOKUP(D347,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D347,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -16124,7 +16124,7 @@
         <v>1804</v>
       </c>
       <c r="H348" t="str">
-        <f>VLOOKUP(D348,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D348,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -16152,7 +16152,7 @@
         <v>1804</v>
       </c>
       <c r="H349" t="str">
-        <f>VLOOKUP(D349,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D349,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -16180,7 +16180,7 @@
         <v>1804</v>
       </c>
       <c r="H350" t="str">
-        <f>VLOOKUP(D350,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D350,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghệ</v>
       </c>
     </row>
@@ -16208,7 +16208,7 @@
         <v>1822</v>
       </c>
       <c r="H351" t="str">
-        <f>VLOOKUP(D351,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D351,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -16236,7 +16236,7 @@
         <v>1822</v>
       </c>
       <c r="H352" t="str">
-        <f>VLOOKUP(D352,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D352,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -16264,7 +16264,7 @@
         <v>1804</v>
       </c>
       <c r="H353" t="str">
-        <f>VLOOKUP(D353,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D353,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -16292,7 +16292,7 @@
         <v>1804</v>
       </c>
       <c r="H354" t="str">
-        <f>VLOOKUP(D354,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D354,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
         <v>1804</v>
       </c>
       <c r="H355" t="str">
-        <f>VLOOKUP(D355,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D355,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -16348,7 +16348,7 @@
         <v>1804</v>
       </c>
       <c r="H356" t="str">
-        <f>VLOOKUP(D356,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D356,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -16376,7 +16376,7 @@
         <v>1804</v>
       </c>
       <c r="H357" t="str">
-        <f>VLOOKUP(D357,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D357,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -16404,7 +16404,7 @@
         <v>1804</v>
       </c>
       <c r="H358" t="str">
-        <f>VLOOKUP(D358,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D358,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -16431,9 +16431,9 @@
       <c r="G359" t="s">
         <v>1822</v>
       </c>
-      <c r="H359" t="e">
-        <f>VLOOKUP(D359,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H359" t="str">
+        <f>VLOOKUP(D359,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
@@ -16460,7 +16460,7 @@
         <v>1804</v>
       </c>
       <c r="H360" t="str">
-        <f>VLOOKUP(D360,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D360,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -16488,7 +16488,7 @@
         <v>1822</v>
       </c>
       <c r="H361" t="str">
-        <f>VLOOKUP(D361,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D361,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -16516,7 +16516,7 @@
         <v>1822</v>
       </c>
       <c r="H362" t="str">
-        <f>VLOOKUP(D362,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D362,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -16544,7 +16544,7 @@
         <v>1804</v>
       </c>
       <c r="H363" t="str">
-        <f>VLOOKUP(D363,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D363,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -16572,7 +16572,7 @@
         <v>1804</v>
       </c>
       <c r="H364" t="str">
-        <f>VLOOKUP(D364,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D364,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -16600,7 +16600,7 @@
         <v>1822</v>
       </c>
       <c r="H365" t="str">
-        <f>VLOOKUP(D365,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D365,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -16628,7 +16628,7 @@
         <v>1822</v>
       </c>
       <c r="H366" t="str">
-        <f>VLOOKUP(D366,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D366,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -16656,7 +16656,7 @@
         <v>1804</v>
       </c>
       <c r="H367" t="str">
-        <f>VLOOKUP(D367,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D367,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -16684,7 +16684,7 @@
         <v>1804</v>
       </c>
       <c r="H368" t="str">
-        <f>VLOOKUP(D368,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D368,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -16712,7 +16712,7 @@
         <v>1822</v>
       </c>
       <c r="H369" t="str">
-        <f>VLOOKUP(D369,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D369,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -16739,9 +16739,9 @@
       <c r="G370" t="s">
         <v>1804</v>
       </c>
-      <c r="H370" t="e">
-        <f>VLOOKUP(D370,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H370" t="str">
+        <f>VLOOKUP(D370,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.25">
@@ -16768,7 +16768,7 @@
         <v>1822</v>
       </c>
       <c r="H371" t="str">
-        <f>VLOOKUP(D371,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D371,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghệ</v>
       </c>
     </row>
@@ -16796,7 +16796,7 @@
         <v>1804</v>
       </c>
       <c r="H372" t="str">
-        <f>VLOOKUP(D372,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D372,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
         <v>1804</v>
       </c>
       <c r="H373" t="str">
-        <f>VLOOKUP(D373,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D373,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -16852,7 +16852,7 @@
         <v>1804</v>
       </c>
       <c r="H374" t="str">
-        <f>VLOOKUP(D374,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D374,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -16880,7 +16880,7 @@
         <v>1822</v>
       </c>
       <c r="H375" t="str">
-        <f>VLOOKUP(D375,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D375,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -16907,9 +16907,9 @@
       <c r="G376" t="s">
         <v>1804</v>
       </c>
-      <c r="H376" t="e">
-        <f>VLOOKUP(D376,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H376" t="str">
+        <f>VLOOKUP(D376,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.25">
@@ -16936,7 +16936,7 @@
         <v>1804</v>
       </c>
       <c r="H377" t="str">
-        <f>VLOOKUP(D377,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D377,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -16964,7 +16964,7 @@
         <v>1822</v>
       </c>
       <c r="H378" t="str">
-        <f>VLOOKUP(D378,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D378,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -16991,9 +16991,9 @@
       <c r="G379" t="s">
         <v>1822</v>
       </c>
-      <c r="H379" t="e">
-        <f>VLOOKUP(D379,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H379" t="str">
+        <f>VLOOKUP(D379,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.25">
@@ -17020,7 +17020,7 @@
         <v>1804</v>
       </c>
       <c r="H380" t="str">
-        <f>VLOOKUP(D380,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D380,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -17048,7 +17048,7 @@
         <v>1804</v>
       </c>
       <c r="H381" t="str">
-        <f>VLOOKUP(D381,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D381,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
         <v>1804</v>
       </c>
       <c r="H382" t="str">
-        <f>VLOOKUP(D382,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D382,name_map!$A$2:$C$33,3,0)</f>
         <v>Thép</v>
       </c>
     </row>
@@ -17104,7 +17104,7 @@
         <v>1804</v>
       </c>
       <c r="H383" t="str">
-        <f>VLOOKUP(D383,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D383,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghệ</v>
       </c>
     </row>
@@ -17132,7 +17132,7 @@
         <v>1804</v>
       </c>
       <c r="H384" t="str">
-        <f>VLOOKUP(D384,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D384,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -17160,7 +17160,7 @@
         <v>1804</v>
       </c>
       <c r="H385" t="str">
-        <f>VLOOKUP(D385,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D385,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghệ</v>
       </c>
     </row>
@@ -17188,7 +17188,7 @@
         <v>1804</v>
       </c>
       <c r="H386" t="str">
-        <f>VLOOKUP(D386,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D386,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -17215,9 +17215,9 @@
       <c r="G387" t="s">
         <v>1804</v>
       </c>
-      <c r="H387" t="e">
-        <f>VLOOKUP(D387,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H387" t="str">
+        <f>VLOOKUP(D387,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.25">
@@ -17244,7 +17244,7 @@
         <v>1822</v>
       </c>
       <c r="H388" t="str">
-        <f>VLOOKUP(D388,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D388,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -17272,7 +17272,7 @@
         <v>1804</v>
       </c>
       <c r="H389" t="str">
-        <f>VLOOKUP(D389,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D389,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghệ</v>
       </c>
     </row>
@@ -17300,7 +17300,7 @@
         <v>1804</v>
       </c>
       <c r="H390" t="str">
-        <f>VLOOKUP(D390,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D390,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -17328,7 +17328,7 @@
         <v>1804</v>
       </c>
       <c r="H391" t="str">
-        <f>VLOOKUP(D391,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D391,name_map!$A$2:$C$33,3,0)</f>
         <v>Du lịch và DV</v>
       </c>
     </row>
@@ -17356,7 +17356,7 @@
         <v>1822</v>
       </c>
       <c r="H392" t="str">
-        <f>VLOOKUP(D392,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D392,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -17384,7 +17384,7 @@
         <v>1804</v>
       </c>
       <c r="H393" t="str">
-        <f>VLOOKUP(D393,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D393,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -17412,7 +17412,7 @@
         <v>1804</v>
       </c>
       <c r="H394" t="str">
-        <f>VLOOKUP(D394,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D394,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -17440,7 +17440,7 @@
         <v>1804</v>
       </c>
       <c r="H395" t="str">
-        <f>VLOOKUP(D395,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D395,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -17468,7 +17468,7 @@
         <v>1804</v>
       </c>
       <c r="H396" t="str">
-        <f>VLOOKUP(D396,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D396,name_map!$A$2:$C$33,3,0)</f>
         <v>BĐS KCN</v>
       </c>
     </row>
@@ -17496,7 +17496,7 @@
         <v>1804</v>
       </c>
       <c r="H397" t="str">
-        <f>VLOOKUP(D397,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D397,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -17524,7 +17524,7 @@
         <v>1804</v>
       </c>
       <c r="H398" t="str">
-        <f>VLOOKUP(D398,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D398,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -17552,7 +17552,7 @@
         <v>1804</v>
       </c>
       <c r="H399" t="str">
-        <f>VLOOKUP(D399,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D399,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -17580,7 +17580,7 @@
         <v>1804</v>
       </c>
       <c r="H400" t="str">
-        <f>VLOOKUP(D400,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D400,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -17608,7 +17608,7 @@
         <v>1804</v>
       </c>
       <c r="H401" t="str">
-        <f>VLOOKUP(D401,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D401,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -17635,9 +17635,9 @@
       <c r="G402" t="s">
         <v>1804</v>
       </c>
-      <c r="H402" t="e">
-        <f>VLOOKUP(D402,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H402" t="str">
+        <f>VLOOKUP(D402,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.25">
@@ -17664,7 +17664,7 @@
         <v>1822</v>
       </c>
       <c r="H403" t="str">
-        <f>VLOOKUP(D403,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D403,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -17692,7 +17692,7 @@
         <v>1804</v>
       </c>
       <c r="H404" t="str">
-        <f>VLOOKUP(D404,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D404,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -17720,7 +17720,7 @@
         <v>1804</v>
       </c>
       <c r="H405" t="str">
-        <f>VLOOKUP(D405,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D405,name_map!$A$2:$C$33,3,0)</f>
         <v>Dệt may</v>
       </c>
     </row>
@@ -17748,7 +17748,7 @@
         <v>1804</v>
       </c>
       <c r="H406" t="str">
-        <f>VLOOKUP(D406,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D406,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -17775,9 +17775,9 @@
       <c r="G407" t="s">
         <v>1822</v>
       </c>
-      <c r="H407" t="e">
-        <f>VLOOKUP(D407,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H407" t="str">
+        <f>VLOOKUP(D407,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.25">
@@ -17804,7 +17804,7 @@
         <v>1822</v>
       </c>
       <c r="H408" t="str">
-        <f>VLOOKUP(D408,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D408,name_map!$A$2:$C$33,3,0)</f>
         <v>Dầu khí</v>
       </c>
     </row>
@@ -17831,9 +17831,9 @@
       <c r="G409" t="s">
         <v>1804</v>
       </c>
-      <c r="H409" t="e">
-        <f>VLOOKUP(D409,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H409" t="str">
+        <f>VLOOKUP(D409,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
@@ -17860,7 +17860,7 @@
         <v>1804</v>
       </c>
       <c r="H410" t="str">
-        <f>VLOOKUP(D410,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D410,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -17888,7 +17888,7 @@
         <v>1804</v>
       </c>
       <c r="H411" t="str">
-        <f>VLOOKUP(D411,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D411,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -17916,7 +17916,7 @@
         <v>1804</v>
       </c>
       <c r="H412" t="str">
-        <f>VLOOKUP(D412,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D412,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
         <v>1804</v>
       </c>
       <c r="H413" t="str">
-        <f>VLOOKUP(D413,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D413,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -17971,9 +17971,9 @@
       <c r="G414" t="s">
         <v>1804</v>
       </c>
-      <c r="H414" t="e">
-        <f>VLOOKUP(D414,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H414" t="str">
+        <f>VLOOKUP(D414,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.25">
@@ -18000,7 +18000,7 @@
         <v>1804</v>
       </c>
       <c r="H415" t="str">
-        <f>VLOOKUP(D415,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D415,name_map!$A$2:$C$33,3,0)</f>
         <v>Công ty tài chính</v>
       </c>
     </row>
@@ -18027,9 +18027,9 @@
       <c r="G416" t="s">
         <v>1804</v>
       </c>
-      <c r="H416" t="e">
-        <f>VLOOKUP(D416,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H416" t="str">
+        <f>VLOOKUP(D416,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.25">
@@ -18056,7 +18056,7 @@
         <v>1804</v>
       </c>
       <c r="H417" t="str">
-        <f>VLOOKUP(D417,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D417,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -18084,7 +18084,7 @@
         <v>1804</v>
       </c>
       <c r="H418" t="str">
-        <f>VLOOKUP(D418,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D418,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -18111,9 +18111,9 @@
       <c r="G419" t="s">
         <v>1822</v>
       </c>
-      <c r="H419" t="e">
-        <f>VLOOKUP(D419,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H419" t="str">
+        <f>VLOOKUP(D419,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.25">
@@ -18140,7 +18140,7 @@
         <v>1804</v>
       </c>
       <c r="H420" t="str">
-        <f>VLOOKUP(D420,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D420,name_map!$A$2:$C$33,3,0)</f>
         <v>Công ty tài chính</v>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
         <v>1804</v>
       </c>
       <c r="H421" t="str">
-        <f>VLOOKUP(D421,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D421,name_map!$A$2:$C$33,3,0)</f>
         <v>BĐS KCN</v>
       </c>
     </row>
@@ -18196,7 +18196,7 @@
         <v>1804</v>
       </c>
       <c r="H422" t="str">
-        <f>VLOOKUP(D422,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D422,name_map!$A$2:$C$33,3,0)</f>
         <v>Thép</v>
       </c>
     </row>
@@ -18224,7 +18224,7 @@
         <v>1804</v>
       </c>
       <c r="H423" t="str">
-        <f>VLOOKUP(D423,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D423,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -18252,7 +18252,7 @@
         <v>1804</v>
       </c>
       <c r="H424" t="str">
-        <f>VLOOKUP(D424,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D424,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -18280,7 +18280,7 @@
         <v>1804</v>
       </c>
       <c r="H425" t="str">
-        <f>VLOOKUP(D425,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D425,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -18308,7 +18308,7 @@
         <v>1804</v>
       </c>
       <c r="H426" t="str">
-        <f>VLOOKUP(D426,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D426,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -18336,7 +18336,7 @@
         <v>1822</v>
       </c>
       <c r="H427" t="str">
-        <f>VLOOKUP(D427,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D427,name_map!$A$2:$C$33,3,0)</f>
         <v>Thép</v>
       </c>
     </row>
@@ -18364,7 +18364,7 @@
         <v>1804</v>
       </c>
       <c r="H428" t="str">
-        <f>VLOOKUP(D428,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D428,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -18391,9 +18391,9 @@
       <c r="G429" t="s">
         <v>1804</v>
       </c>
-      <c r="H429" t="e">
-        <f>VLOOKUP(D429,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H429" t="str">
+        <f>VLOOKUP(D429,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bán lẻ</v>
       </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.25">
@@ -18420,7 +18420,7 @@
         <v>1822</v>
       </c>
       <c r="H430" t="str">
-        <f>VLOOKUP(D430,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D430,name_map!$A$2:$C$33,3,0)</f>
         <v>Dệt may</v>
       </c>
     </row>
@@ -18448,7 +18448,7 @@
         <v>1804</v>
       </c>
       <c r="H431" t="str">
-        <f>VLOOKUP(D431,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D431,name_map!$A$2:$C$33,3,0)</f>
         <v>Y tế</v>
       </c>
     </row>
@@ -18476,7 +18476,7 @@
         <v>1804</v>
       </c>
       <c r="H432" t="str">
-        <f>VLOOKUP(D432,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D432,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -18504,7 +18504,7 @@
         <v>1804</v>
       </c>
       <c r="H433" t="str">
-        <f>VLOOKUP(D433,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D433,name_map!$A$2:$C$33,3,0)</f>
         <v>Thép</v>
       </c>
     </row>
@@ -18532,7 +18532,7 @@
         <v>1822</v>
       </c>
       <c r="H434" t="str">
-        <f>VLOOKUP(D434,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D434,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -18560,7 +18560,7 @@
         <v>1804</v>
       </c>
       <c r="H435" t="str">
-        <f>VLOOKUP(D435,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D435,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
         <v>1822</v>
       </c>
       <c r="H436" t="str">
-        <f>VLOOKUP(D436,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D436,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -18616,7 +18616,7 @@
         <v>1804</v>
       </c>
       <c r="H437" t="str">
-        <f>VLOOKUP(D437,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D437,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
         <v>1804</v>
       </c>
       <c r="H438" t="str">
-        <f>VLOOKUP(D438,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D438,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -18672,7 +18672,7 @@
         <v>1822</v>
       </c>
       <c r="H439" t="str">
-        <f>VLOOKUP(D439,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D439,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -18699,9 +18699,9 @@
       <c r="G440" t="s">
         <v>1804</v>
       </c>
-      <c r="H440" t="e">
-        <f>VLOOKUP(D440,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H440" t="str">
+        <f>VLOOKUP(D440,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bán lẻ</v>
       </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.25">
@@ -18728,7 +18728,7 @@
         <v>1804</v>
       </c>
       <c r="H441" t="str">
-        <f>VLOOKUP(D441,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D441,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -18756,7 +18756,7 @@
         <v>1804</v>
       </c>
       <c r="H442" t="str">
-        <f>VLOOKUP(D442,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D442,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -18784,7 +18784,7 @@
         <v>1804</v>
       </c>
       <c r="H443" t="str">
-        <f>VLOOKUP(D443,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D443,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -18812,7 +18812,7 @@
         <v>1804</v>
       </c>
       <c r="H444" t="str">
-        <f>VLOOKUP(D444,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D444,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -18840,7 +18840,7 @@
         <v>1804</v>
       </c>
       <c r="H445" t="str">
-        <f>VLOOKUP(D445,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D445,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -18868,7 +18868,7 @@
         <v>1822</v>
       </c>
       <c r="H446" t="str">
-        <f>VLOOKUP(D446,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D446,name_map!$A$2:$C$33,3,0)</f>
         <v>Công ty tài chính</v>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
         <v>1804</v>
       </c>
       <c r="H447" t="str">
-        <f>VLOOKUP(D447,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D447,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -18924,7 +18924,7 @@
         <v>1822</v>
       </c>
       <c r="H448" t="str">
-        <f>VLOOKUP(D448,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D448,name_map!$A$2:$C$33,3,0)</f>
         <v>Thép</v>
       </c>
     </row>
@@ -18952,7 +18952,7 @@
         <v>1822</v>
       </c>
       <c r="H449" t="str">
-        <f>VLOOKUP(D449,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D449,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -18980,7 +18980,7 @@
         <v>1804</v>
       </c>
       <c r="H450" t="str">
-        <f>VLOOKUP(D450,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D450,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -19008,7 +19008,7 @@
         <v>1804</v>
       </c>
       <c r="H451" t="str">
-        <f>VLOOKUP(D451,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D451,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -19036,7 +19036,7 @@
         <v>1804</v>
       </c>
       <c r="H452" t="str">
-        <f>VLOOKUP(D452,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D452,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -19064,7 +19064,7 @@
         <v>1804</v>
       </c>
       <c r="H453" t="str">
-        <f>VLOOKUP(D453,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D453,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -19092,7 +19092,7 @@
         <v>1804</v>
       </c>
       <c r="H454" t="str">
-        <f>VLOOKUP(D454,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D454,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -19120,7 +19120,7 @@
         <v>1804</v>
       </c>
       <c r="H455" t="str">
-        <f>VLOOKUP(D455,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D455,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -19147,9 +19147,9 @@
       <c r="G456" t="s">
         <v>1804</v>
       </c>
-      <c r="H456" t="e">
-        <f>VLOOKUP(D456,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H456" t="str">
+        <f>VLOOKUP(D456,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.25">
@@ -19176,7 +19176,7 @@
         <v>1822</v>
       </c>
       <c r="H457" t="str">
-        <f>VLOOKUP(D457,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D457,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -19204,7 +19204,7 @@
         <v>1804</v>
       </c>
       <c r="H458" t="str">
-        <f>VLOOKUP(D458,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D458,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -19232,7 +19232,7 @@
         <v>1804</v>
       </c>
       <c r="H459" t="str">
-        <f>VLOOKUP(D459,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D459,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -19260,7 +19260,7 @@
         <v>1804</v>
       </c>
       <c r="H460" t="str">
-        <f>VLOOKUP(D460,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D460,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -19288,7 +19288,7 @@
         <v>1804</v>
       </c>
       <c r="H461" t="str">
-        <f>VLOOKUP(D461,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D461,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -19316,7 +19316,7 @@
         <v>1822</v>
       </c>
       <c r="H462" t="str">
-        <f>VLOOKUP(D462,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D462,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -19343,9 +19343,9 @@
       <c r="G463" t="s">
         <v>1804</v>
       </c>
-      <c r="H463" t="e">
-        <f>VLOOKUP(D463,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H463" t="str">
+        <f>VLOOKUP(D463,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.25">
@@ -19372,7 +19372,7 @@
         <v>1804</v>
       </c>
       <c r="H464" t="str">
-        <f>VLOOKUP(D464,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D464,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -19400,7 +19400,7 @@
         <v>1822</v>
       </c>
       <c r="H465" t="str">
-        <f>VLOOKUP(D465,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D465,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -19428,7 +19428,7 @@
         <v>1822</v>
       </c>
       <c r="H466" t="str">
-        <f>VLOOKUP(D466,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D466,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -19456,7 +19456,7 @@
         <v>1804</v>
       </c>
       <c r="H467" t="str">
-        <f>VLOOKUP(D467,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D467,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -19484,7 +19484,7 @@
         <v>1804</v>
       </c>
       <c r="H468" t="str">
-        <f>VLOOKUP(D468,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D468,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -19512,7 +19512,7 @@
         <v>1804</v>
       </c>
       <c r="H469" t="str">
-        <f>VLOOKUP(D469,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D469,name_map!$A$2:$C$33,3,0)</f>
         <v>BĐS KCN</v>
       </c>
     </row>
@@ -19540,7 +19540,7 @@
         <v>1804</v>
       </c>
       <c r="H470" t="str">
-        <f>VLOOKUP(D470,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D470,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghệ</v>
       </c>
     </row>
@@ -19568,7 +19568,7 @@
         <v>1822</v>
       </c>
       <c r="H471" t="str">
-        <f>VLOOKUP(D471,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D471,name_map!$A$2:$C$33,3,0)</f>
         <v>Thép</v>
       </c>
     </row>
@@ -19596,7 +19596,7 @@
         <v>1822</v>
       </c>
       <c r="H472" t="str">
-        <f>VLOOKUP(D472,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D472,name_map!$A$2:$C$33,3,0)</f>
         <v>Dệt may</v>
       </c>
     </row>
@@ -19624,7 +19624,7 @@
         <v>1804</v>
       </c>
       <c r="H473" t="str">
-        <f>VLOOKUP(D473,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D473,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -19652,7 +19652,7 @@
         <v>1804</v>
       </c>
       <c r="H474" t="str">
-        <f>VLOOKUP(D474,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D474,name_map!$A$2:$C$33,3,0)</f>
         <v>Thuỷ sản</v>
       </c>
     </row>
@@ -19680,7 +19680,7 @@
         <v>1804</v>
       </c>
       <c r="H475" t="str">
-        <f>VLOOKUP(D475,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D475,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -19707,9 +19707,9 @@
       <c r="G476" t="s">
         <v>1822</v>
       </c>
-      <c r="H476" t="e">
-        <f>VLOOKUP(D476,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H476" t="str">
+        <f>VLOOKUP(D476,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.25">
@@ -19735,9 +19735,9 @@
       <c r="G477" t="s">
         <v>1804</v>
       </c>
-      <c r="H477" t="e">
-        <f>VLOOKUP(D477,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H477" t="str">
+        <f>VLOOKUP(D477,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.25">
@@ -19764,7 +19764,7 @@
         <v>1804</v>
       </c>
       <c r="H478" t="str">
-        <f>VLOOKUP(D478,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D478,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -19791,9 +19791,9 @@
       <c r="G479" t="s">
         <v>1804</v>
       </c>
-      <c r="H479" t="e">
-        <f>VLOOKUP(D479,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H479" t="str">
+        <f>VLOOKUP(D479,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
@@ -19820,7 +19820,7 @@
         <v>1804</v>
       </c>
       <c r="H480" t="str">
-        <f>VLOOKUP(D480,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D480,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -19848,7 +19848,7 @@
         <v>1822</v>
       </c>
       <c r="H481" t="str">
-        <f>VLOOKUP(D481,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D481,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -19876,7 +19876,7 @@
         <v>1804</v>
       </c>
       <c r="H482" t="str">
-        <f>VLOOKUP(D482,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D482,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -19904,7 +19904,7 @@
         <v>1822</v>
       </c>
       <c r="H483" t="str">
-        <f>VLOOKUP(D483,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D483,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -19932,7 +19932,7 @@
         <v>1804</v>
       </c>
       <c r="H484" t="str">
-        <f>VLOOKUP(D484,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D484,name_map!$A$2:$C$33,3,0)</f>
         <v>Du lịch và DV</v>
       </c>
     </row>
@@ -19960,7 +19960,7 @@
         <v>1804</v>
       </c>
       <c r="H485" t="str">
-        <f>VLOOKUP(D485,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D485,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
         <v>1804</v>
       </c>
       <c r="H486" t="str">
-        <f>VLOOKUP(D486,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D486,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -20016,7 +20016,7 @@
         <v>1804</v>
       </c>
       <c r="H487" t="str">
-        <f>VLOOKUP(D487,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D487,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -20044,7 +20044,7 @@
         <v>1804</v>
       </c>
       <c r="H488" t="str">
-        <f>VLOOKUP(D488,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D488,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -20072,7 +20072,7 @@
         <v>1804</v>
       </c>
       <c r="H489" t="str">
-        <f>VLOOKUP(D489,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D489,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -20100,7 +20100,7 @@
         <v>1804</v>
       </c>
       <c r="H490" t="str">
-        <f>VLOOKUP(D490,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D490,name_map!$A$2:$C$33,3,0)</f>
         <v>Hàng tiêu dùng</v>
       </c>
     </row>
@@ -20128,7 +20128,7 @@
         <v>1822</v>
       </c>
       <c r="H491" t="str">
-        <f>VLOOKUP(D491,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D491,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -20156,7 +20156,7 @@
         <v>1804</v>
       </c>
       <c r="H492" t="str">
-        <f>VLOOKUP(D492,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D492,name_map!$A$2:$C$33,3,0)</f>
         <v>Xây dựng</v>
       </c>
     </row>
@@ -20184,7 +20184,7 @@
         <v>1804</v>
       </c>
       <c r="H493" t="str">
-        <f>VLOOKUP(D493,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D493,name_map!$A$2:$C$33,3,0)</f>
         <v>Du lịch và DV</v>
       </c>
     </row>
@@ -20212,7 +20212,7 @@
         <v>1822</v>
       </c>
       <c r="H494" t="str">
-        <f>VLOOKUP(D494,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D494,name_map!$A$2:$C$33,3,0)</f>
         <v>Thuỷ sản</v>
       </c>
     </row>
@@ -20240,7 +20240,7 @@
         <v>1804</v>
       </c>
       <c r="H495" t="str">
-        <f>VLOOKUP(D495,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D495,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -20268,7 +20268,7 @@
         <v>1804</v>
       </c>
       <c r="H496" t="str">
-        <f>VLOOKUP(D496,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D496,name_map!$A$2:$C$33,3,0)</f>
         <v>Hoá chất</v>
       </c>
     </row>
@@ -20296,7 +20296,7 @@
         <v>1804</v>
       </c>
       <c r="H497" t="str">
-        <f>VLOOKUP(D497,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D497,name_map!$A$2:$C$33,3,0)</f>
         <v>Bảo hiểm</v>
       </c>
     </row>
@@ -20324,7 +20324,7 @@
         <v>1804</v>
       </c>
       <c r="H498" t="str">
-        <f>VLOOKUP(D498,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D498,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -20352,7 +20352,7 @@
         <v>1804</v>
       </c>
       <c r="H499" t="str">
-        <f>VLOOKUP(D499,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D499,name_map!$A$2:$C$33,3,0)</f>
         <v>Thực phẩm</v>
       </c>
     </row>
@@ -20380,7 +20380,7 @@
         <v>1822</v>
       </c>
       <c r="H500" t="str">
-        <f>VLOOKUP(D500,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D500,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -20408,7 +20408,7 @@
         <v>1804</v>
       </c>
       <c r="H501" t="str">
-        <f>VLOOKUP(D501,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D501,name_map!$A$2:$C$33,3,0)</f>
         <v>Ngân hàng</v>
       </c>
     </row>
@@ -20436,7 +20436,7 @@
         <v>1822</v>
       </c>
       <c r="H502" t="str">
-        <f>VLOOKUP(D502,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D502,name_map!$A$2:$C$33,3,0)</f>
         <v>Khoáng sản</v>
       </c>
     </row>
@@ -20463,9 +20463,9 @@
       <c r="G503" t="s">
         <v>1804</v>
       </c>
-      <c r="H503" t="e">
-        <f>VLOOKUP(D503,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H503" t="str">
+        <f>VLOOKUP(D503,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.25">
@@ -20491,9 +20491,9 @@
       <c r="G504" t="s">
         <v>1804</v>
       </c>
-      <c r="H504" t="e">
-        <f>VLOOKUP(D504,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H504" t="str">
+        <f>VLOOKUP(D504,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -20519,9 +20519,9 @@
       <c r="G505" t="s">
         <v>1804</v>
       </c>
-      <c r="H505" t="e">
-        <f>VLOOKUP(D505,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H505" t="str">
+        <f>VLOOKUP(D505,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
@@ -20547,9 +20547,9 @@
       <c r="G506" t="s">
         <v>1804</v>
       </c>
-      <c r="H506" t="e">
-        <f>VLOOKUP(D506,name_map!$A$4:$C$24,3,0)</f>
-        <v>#N/A</v>
+      <c r="H506" t="str">
+        <f>VLOOKUP(D506,name_map!$A$2:$C$33,3,0)</f>
+        <v>Bất động sản</v>
       </c>
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.25">
@@ -20576,7 +20576,7 @@
         <v>1804</v>
       </c>
       <c r="H507" t="str">
-        <f>VLOOKUP(D507,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D507,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -20604,7 +20604,7 @@
         <v>1804</v>
       </c>
       <c r="H508" t="str">
-        <f>VLOOKUP(D508,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D508,name_map!$A$2:$C$33,3,0)</f>
         <v>DV hạ tầng</v>
       </c>
     </row>
@@ -20632,7 +20632,7 @@
         <v>1804</v>
       </c>
       <c r="H509" t="str">
-        <f>VLOOKUP(D509,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D509,name_map!$A$2:$C$33,3,0)</f>
         <v>Du lịch và DV</v>
       </c>
     </row>
@@ -20660,7 +20660,7 @@
         <v>1804</v>
       </c>
       <c r="H510" t="str">
-        <f>VLOOKUP(D510,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D510,name_map!$A$2:$C$33,3,0)</f>
         <v>Vận tải</v>
       </c>
     </row>
@@ -20688,7 +20688,7 @@
         <v>1804</v>
       </c>
       <c r="H511" t="str">
-        <f>VLOOKUP(D511,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D511,name_map!$A$2:$C$33,3,0)</f>
         <v>Công nghiệp</v>
       </c>
     </row>
@@ -20716,7 +20716,7 @@
         <v>1804</v>
       </c>
       <c r="H512" t="str">
-        <f>VLOOKUP(D512,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D512,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -20744,7 +20744,7 @@
         <v>1804</v>
       </c>
       <c r="H513" t="str">
-        <f>VLOOKUP(D513,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D513,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -20772,7 +20772,7 @@
         <v>1822</v>
       </c>
       <c r="H514" t="str">
-        <f>VLOOKUP(D514,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D514,name_map!$A$2:$C$33,3,0)</f>
         <v>Chứng khoán</v>
       </c>
     </row>
@@ -20800,7 +20800,7 @@
         <v>1822</v>
       </c>
       <c r="H515" t="str">
-        <f>VLOOKUP(D515,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D515,name_map!$A$2:$C$33,3,0)</f>
         <v>Vật liệu xây dựng</v>
       </c>
     </row>
@@ -20828,7 +20828,7 @@
         <v>1804</v>
       </c>
       <c r="H516" t="str">
-        <f>VLOOKUP(D516,name_map!$A$4:$C$24,3,0)</f>
+        <f>VLOOKUP(D516,name_map!$A$2:$C$33,3,0)</f>
         <v>Du lịch và DV</v>
       </c>
     </row>

--- a/data/t2m_classification.xlsx
+++ b/data/t2m_classification.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\t2m-project\t2m-pycode\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BDCAB0-3675-46A4-B231-A54C26918719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9B57C5-7657-472D-BF69-D50F74B2CF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18715,7 +18715,7 @@
         <v>736</v>
       </c>
       <c r="D441" t="s">
-        <v>880</v>
+        <v>524</v>
       </c>
       <c r="E441" t="str">
         <f>VLOOKUP(D441,name_map!$A$2:$D$24,2,0)</f>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="H441" t="str">
         <f>VLOOKUP(D441,name_map!$A$2:$C$33,3,0)</f>
-        <v>Hàng tiêu dùng</v>
+        <v>Công nghệ</v>
       </c>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.25">

--- a/data/t2m_classification.xlsx
+++ b/data/t2m_classification.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\t2m-project\t2m-pycode\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9B57C5-7657-472D-BF69-D50F74B2CF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163A6E90-AB53-4E31-A403-35AE3B172444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6759,11 +6759,11 @@
         <v>1423</v>
       </c>
       <c r="D14" t="s">
-        <v>1423</v>
+        <v>1731</v>
       </c>
       <c r="E14" t="str">
         <f>VLOOKUP(D14,name_map!$A$2:$D$24,2,0)</f>
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="F14" t="s">
         <v>1815</v>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="H14" t="str">
         <f>VLOOKUP(D14,name_map!$A$2:$C$33,3,0)</f>
-        <v>Công nghiệp</v>
+        <v>Du lịch và DV</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
